--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7328,7 +7328,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12625,16 +12625,16 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12787,10 +12787,10 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1269</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -13417,16 +13417,16 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O66" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>0.08256815648230102</v>
+        <v>0.09125954137517482</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13579,10 +13579,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O67" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1271</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>72</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>32</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.355247753113469</v>
       </c>
@@ -1554,9 +1548,6 @@
       <c r="O6" t="n">
         <v>9</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.1600928253777724</v>
       </c>
@@ -1950,9 +1941,6 @@
       <c r="O8" t="n">
         <v>18</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.3184156486431911</v>
       </c>
@@ -2346,9 +2334,6 @@
       <c r="O10" t="n">
         <v>98</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.4258778597508158</v>
       </c>
@@ -2595,7 +2580,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -2742,9 +2727,6 @@
       <c r="O12" t="n">
         <v>59</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3135,9 +3117,6 @@
       <c r="O14" t="n">
         <v>28</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.3108417839742854</v>
       </c>
@@ -3531,9 +3510,6 @@
       <c r="O16" t="n">
         <v>13</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.2312451922123379</v>
       </c>
@@ -3927,9 +3903,6 @@
       <c r="O18" t="n">
         <v>10</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.1768975825795506</v>
       </c>
@@ -4323,9 +4296,6 @@
       <c r="O20" t="n">
         <v>83</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.3606924730542624</v>
       </c>
@@ -4572,7 +4542,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4719,9 +4689,6 @@
       <c r="O22" t="n">
         <v>53</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5112,9 +5079,6 @@
       <c r="O24" t="n">
         <v>32</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.355247753113469</v>
       </c>
@@ -5508,9 +5472,6 @@
       <c r="O26" t="n">
         <v>19</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.3379737424641861</v>
       </c>
@@ -5904,9 +5865,6 @@
       <c r="O28" t="n">
         <v>21</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.3714849234170563</v>
       </c>
@@ -6300,9 +6258,6 @@
       <c r="O30" t="n">
         <v>106</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.460643399322311</v>
       </c>
@@ -6549,7 +6504,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6696,9 +6651,6 @@
       <c r="O32" t="n">
         <v>50</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7089,9 +7041,6 @@
       <c r="O34" t="n">
         <v>25</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.2775373071198977</v>
       </c>
@@ -7485,9 +7434,6 @@
       <c r="O36" t="n">
         <v>12</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.2134571005036965</v>
       </c>
@@ -7881,9 +7827,6 @@
       <c r="O38" t="n">
         <v>11</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.1945873408375057</v>
       </c>
@@ -8277,9 +8220,6 @@
       <c r="O40" t="n">
         <v>82</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.3563467806078255</v>
       </c>
@@ -8526,7 +8466,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8673,9 +8613,6 @@
       <c r="O42" t="n">
         <v>50</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9066,9 +9003,6 @@
       <c r="O44" t="n">
         <v>13</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.2312451922123379</v>
       </c>
@@ -9462,9 +9396,6 @@
       <c r="O46" t="n">
         <v>22</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.3891746816750113</v>
       </c>
@@ -9858,9 +9789,6 @@
       <c r="O48" t="n">
         <v>93</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.4041493975186313</v>
       </c>
@@ -10107,7 +10035,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10254,9 +10182,6 @@
       <c r="O50" t="n">
         <v>14</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2490332839209793</v>
       </c>
@@ -10650,9 +10575,6 @@
       <c r="O52" t="n">
         <v>16</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.283036132127281</v>
       </c>
@@ -11046,9 +10968,6 @@
       <c r="O54" t="n">
         <v>100</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.4345692446436896</v>
       </c>
@@ -11295,7 +11214,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11442,9 +11361,6 @@
       <c r="O56" t="n">
         <v>7</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.1245166419604896</v>
       </c>
@@ -11838,9 +11754,6 @@
       <c r="O58" t="n">
         <v>13</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.2299668573534158</v>
       </c>
@@ -12234,9 +12147,6 @@
       <c r="O60" t="n">
         <v>89</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.3867666277328837</v>
       </c>
@@ -12483,7 +12393,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12630,9 +12540,6 @@
       <c r="O62" t="n">
         <v>2</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -13021,16 +12928,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13183,10 +13087,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13417,16 +13321,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="O66" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R66" t="n">
-        <v>0.09125954137517482</v>
+        <v>0.1216793885002331</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13579,10 +13480,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="O67" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13671,7 +13572,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13924,7 +13825,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1273</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -13321,13 +13321,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O66" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R66" t="n">
-        <v>0.1216793885002331</v>
+        <v>0.1347164658395438</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O67" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1281</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -12535,13 +12535,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R62" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12694,10 +12694,10 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
@@ -13321,13 +13321,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O66" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R66" t="n">
-        <v>0.1347164658395438</v>
+        <v>0.1390621582859807</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13480,10 +13480,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O67" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -13825,7 +13825,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1284</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O22" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O42" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="O43" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
@@ -10138,12 +10138,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -10177,22 +10177,19 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="O50" t="n">
-        <v>14</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0.2490332839209793</v>
+        <v>71</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -10212,12 +10209,12 @@
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -10225,47 +10222,47 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10297,12 +10294,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -10336,29 +10333,29 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="O51" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -10368,7 +10365,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -10383,7 +10380,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -10418,17 +10415,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>PHO IDTO current-year monthly HIV counts include eligible carrier/carrier and case/confirmed encounters and are classified by Encounter Date (Reported Date). The series includes patients who progressed to AIDS and is not mutually exclusive with the AIDS series.</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10446,12 +10443,12 @@
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -10459,47 +10456,47 @@
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10531,12 +10528,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -10570,13 +10567,13 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O52" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R52" t="n">
-        <v>0.283036132127281</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -10585,7 +10582,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -10605,12 +10602,12 @@
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT52" t="n">
@@ -10618,47 +10615,47 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -10690,12 +10687,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10729,29 +10726,29 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O53" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -10776,7 +10773,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -10811,17 +10808,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10839,12 +10836,12 @@
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT53" t="n">
@@ -10852,47 +10849,47 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -10924,12 +10921,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -10963,13 +10960,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="O54" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="R54" t="n">
-        <v>0.4345692446436896</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -10978,7 +10975,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -11003,7 +11000,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -11016,42 +11013,42 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11080,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11122,29 +11119,29 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="O55" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -11154,7 +11151,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -11169,7 +11166,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11184,7 +11181,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
@@ -11204,17 +11201,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11237,7 +11234,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -11250,42 +11247,42 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -11317,12 +11314,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -11347,22 +11344,22 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N56" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="O56" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="R56" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.4345692446436896</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11371,7 +11368,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -11391,12 +11388,12 @@
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT56" t="n">
@@ -11404,47 +11401,47 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11476,12 +11473,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -11506,38 +11503,38 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="O57" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -11547,7 +11544,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -11562,7 +11559,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -11577,7 +11574,7 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
@@ -11597,12 +11594,12 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
@@ -11625,12 +11622,12 @@
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT57" t="n">
@@ -11638,47 +11635,47 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11710,12 +11707,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11749,13 +11746,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O58" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R58" t="n">
-        <v>0.2299668573534158</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11764,7 +11761,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -11784,12 +11781,12 @@
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT58" t="n">
@@ -11797,47 +11794,47 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11869,12 +11866,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -11908,29 +11905,29 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O59" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -11955,7 +11952,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -11990,17 +11987,17 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12018,12 +12015,12 @@
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT59" t="n">
@@ -12031,47 +12028,47 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12103,12 +12100,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12142,13 +12139,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="O60" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="R60" t="n">
-        <v>0.3867666277328837</v>
+        <v>0.2299668573534158</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12157,7 +12154,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -12182,7 +12179,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -12195,42 +12192,42 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12259,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12301,29 +12298,29 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="O61" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -12333,7 +12330,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -12348,7 +12345,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -12363,7 +12360,7 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
@@ -12383,17 +12380,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12416,7 +12413,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -12429,42 +12426,42 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12496,12 +12493,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12526,22 +12523,22 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="O62" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="R62" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.3867666277328837</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12550,7 +12547,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -12570,12 +12567,12 @@
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT62" t="n">
@@ -12583,47 +12580,47 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12655,12 +12652,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12685,38 +12682,38 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="O63" t="n">
-        <v>3</v>
+        <v>89</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -12726,7 +12723,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -12741,7 +12738,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -12756,7 +12753,7 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr">
@@ -12776,12 +12773,12 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
@@ -12804,12 +12801,12 @@
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT63" t="n">
@@ -12817,47 +12814,47 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12889,12 +12886,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -12928,13 +12925,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -12943,7 +12940,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -12963,12 +12960,12 @@
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT64" t="n">
@@ -12976,47 +12973,47 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13048,12 +13045,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -13087,29 +13084,29 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -13134,7 +13131,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -13169,17 +13166,17 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13197,12 +13194,12 @@
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT65" t="n">
@@ -13210,47 +13207,47 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13282,12 +13279,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -13321,13 +13318,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>0.1390621582859807</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13336,7 +13333,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -13361,7 +13358,7 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -13374,42 +13371,42 @@
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13441,12 +13438,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -13480,29 +13477,29 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -13512,7 +13509,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -13527,7 +13524,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -13542,7 +13539,7 @@
       </c>
       <c r="AF67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG67" t="inlineStr">
@@ -13562,17 +13559,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13595,7 +13592,7 @@
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
@@ -13608,40 +13605,433 @@
       </c>
       <c r="AV67" t="inlineStr">
         <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA67" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB67" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC67" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N68" t="n">
+        <v>32</v>
+      </c>
+      <c r="O68" t="n">
+        <v>32</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.1390621582859807</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AT68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="AW67" t="inlineStr">
+      <c r="AW68" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
+      <c r="AX68" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="AY67" t="inlineStr">
+      <c r="AY68" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
+      <c r="AZ68" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="BA67" t="inlineStr">
+      <c r="BA68" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="BB67" t="inlineStr">
+      <c r="BB68" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="BC67" t="inlineStr">
+      <c r="BC68" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>32</v>
+      </c>
+      <c r="O69" t="n">
+        <v>32</v>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AT69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -13763,7 +14153,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -13773,7 +14163,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
@@ -13793,7 +14183,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13">
@@ -13825,7 +14215,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1286</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -13711,13 +13711,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="O68" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="R68" t="n">
-        <v>0.1390621582859807</v>
+        <v>0.1607906205181651</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13870,10 +13870,10 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="O69" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1358</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -12925,13 +12925,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R64" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13084,10 +13084,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O65" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1363</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13477,10 +13477,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -12925,13 +12925,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R64" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13084,10 +13084,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O66" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="R66" t="n">
-        <v>0.03537951651591013</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13477,10 +13477,10 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O67" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1367</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12925,13 +12925,13 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O64" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R64" t="n">
-        <v>0.142304733669131</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13084,10 +13084,10 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14215,7 +14215,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1374</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1581,17 +1581,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1807,7 +1812,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1815,17 +1820,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1966,7 +1976,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1974,17 +1984,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2200,7 +2215,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2208,17 +2223,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2570,7 +2590,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3353,7 +3373,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3535,7 +3555,7 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
@@ -3543,17 +3563,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS16" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
@@ -3769,7 +3794,7 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -3777,17 +3802,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
@@ -3928,7 +3958,7 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
@@ -3936,17 +3966,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS18" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
@@ -4162,7 +4197,7 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
@@ -4170,17 +4205,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS19" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
@@ -4532,7 +4572,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5315,7 +5355,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5497,7 +5537,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5505,17 +5545,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5731,7 +5776,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5739,17 +5784,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5890,7 +5940,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5898,17 +5948,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -6124,7 +6179,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -6132,17 +6187,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -6494,7 +6554,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7277,7 +7337,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7459,7 +7519,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -7467,17 +7527,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -7693,7 +7758,7 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
@@ -7701,17 +7766,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS37" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
@@ -7852,7 +7922,7 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
@@ -7860,17 +7930,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS38" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
@@ -8086,7 +8161,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -8094,17 +8169,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -8456,7 +8536,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9028,7 +9108,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -9036,17 +9116,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -9262,7 +9347,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -9270,17 +9355,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -9421,7 +9511,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -9429,17 +9519,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -9655,7 +9750,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -9663,17 +9758,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -10025,7 +10125,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10597,7 +10697,7 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
@@ -10605,17 +10705,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS52" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
@@ -10831,7 +10936,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -10839,17 +10944,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10990,7 +11100,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -10998,17 +11108,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS54" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -11224,7 +11339,7 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
@@ -11232,17 +11347,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS55" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
@@ -11594,7 +11714,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11776,7 +11896,7 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
@@ -11784,17 +11904,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS58" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
@@ -12010,7 +12135,7 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
@@ -12018,17 +12143,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS59" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
@@ -12169,7 +12299,7 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
@@ -12177,17 +12307,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS60" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
@@ -12403,7 +12538,7 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
@@ -12411,17 +12546,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS61" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
@@ -12773,7 +12913,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -12955,7 +13095,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -12963,17 +13103,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -13189,7 +13334,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -13197,17 +13342,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -13348,7 +13498,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -13356,17 +13506,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -13582,7 +13737,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -13590,17 +13745,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -13952,7 +14112,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">

--- a/diseases/d162/2026-2029.xlsx
+++ b/diseases/d162/2026-2029.xlsx
@@ -9039,12 +9039,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -9078,13 +9078,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="O44" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="R44" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.3219432762590813</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CH_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -9108,70 +9108,65 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CH_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -9203,12 +9198,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -9242,29 +9237,29 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="O45" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CH_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CH_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CH_FOPH_IDD</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>Human Immunodeficiency Virus (HIV)</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -9274,7 +9269,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -9289,7 +9284,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CH:national</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
@@ -9304,7 +9299,7 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
@@ -9324,17 +9319,17 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>Source-reported HIV diagnoses at any reported stage.</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9347,70 +9342,65 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CH_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -9442,12 +9432,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -9481,13 +9471,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="O46" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="R46" t="n">
-        <v>0.3891746816750113</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -9496,7 +9486,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -9516,7 +9506,7 @@
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
@@ -9526,7 +9516,7 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT46" t="n">
@@ -9534,47 +9524,47 @@
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9596,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -9645,29 +9635,29 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="O47" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -9692,7 +9682,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr">
@@ -9727,17 +9717,17 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -9755,7 +9745,7 @@
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
@@ -9765,7 +9755,7 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT47" t="n">
@@ -9773,47 +9763,47 @@
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -9845,12 +9835,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -9884,13 +9874,13 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="O48" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="R48" t="n">
-        <v>0.4041493975186313</v>
+        <v>0.3891746816750113</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -9899,7 +9889,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -9914,7 +9904,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -9922,57 +9912,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10004,12 +9999,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -10043,29 +10038,29 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="O49" t="n">
-        <v>93</v>
+        <v>22</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -10075,7 +10070,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -10090,7 +10085,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr">
@@ -10105,7 +10100,7 @@
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
@@ -10125,17 +10120,17 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10148,7 +10143,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -10156,57 +10151,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -10238,12 +10238,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -10268,28 +10268,31 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="O50" t="n">
-        <v>71</v>
+        <v>93</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.4041493975186313</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -10314,7 +10317,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT50" t="n">
@@ -10327,42 +10330,42 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10394,12 +10397,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -10424,38 +10427,38 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="O51" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>HIV</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
@@ -10480,7 +10483,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>country:CA-ON:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr">
@@ -10495,7 +10498,7 @@
       </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG51" t="inlineStr">
@@ -10515,17 +10518,17 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>PHO_IDTO_2026_07</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>PHO IDTO current-year monthly HIV counts include eligible carrier/carrier and case/confirmed encounters and are classified by Encounter Date (Reported Date). The series includes patients who progressed to AIDS and is not mutually exclusive with the AIDS series.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10548,7 +10551,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT51" t="n">
@@ -10561,42 +10564,42 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10631,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -10667,22 +10670,19 @@
         </is>
       </c>
       <c r="N52" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="O52" t="n">
-        <v>14</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.2490332839209793</v>
+        <v>71</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -10697,70 +10697,65 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -10792,12 +10787,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -10831,29 +10826,29 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="O53" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>HIV</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -10863,7 +10858,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -10878,7 +10873,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr">
@@ -10913,17 +10908,17 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>PHO IDTO current-year monthly HIV counts include eligible carrier/carrier and case/confirmed encounters and are classified by Encounter Date (Reported Date). The series includes patients who progressed to AIDS and is not mutually exclusive with the AIDS series.</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -10936,70 +10931,65 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_CA_ON_PHO_IDTO_HIV_MONTHLY</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -11031,12 +11021,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -11070,13 +11060,13 @@
         </is>
       </c>
       <c r="N54" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O54" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R54" t="n">
-        <v>0.283036132127281</v>
+        <v>0.2490332839209793</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -11085,7 +11075,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -11105,7 +11095,7 @@
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
@@ -11115,7 +11105,7 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT54" t="n">
@@ -11123,47 +11113,47 @@
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11195,12 +11185,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -11234,29 +11224,29 @@
         </is>
       </c>
       <c r="N55" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O55" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -11281,7 +11271,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr">
@@ -11316,17 +11306,17 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11344,7 +11334,7 @@
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
@@ -11354,7 +11344,7 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT55" t="n">
@@ -11362,47 +11352,47 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11434,12 +11424,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -11473,13 +11463,13 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="O56" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="R56" t="n">
-        <v>0.4345692446436896</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -11488,7 +11478,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -11503,7 +11493,7 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
@@ -11511,57 +11501,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -11593,12 +11588,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -11632,29 +11627,29 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="O57" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -11664,7 +11659,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -11679,7 +11674,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr">
@@ -11694,7 +11689,7 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
@@ -11714,17 +11709,17 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -11737,7 +11732,7 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
@@ -11745,57 +11740,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -11827,12 +11827,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -11857,22 +11857,22 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="O58" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="R58" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.4345692446436896</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -11896,70 +11896,65 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -11991,12 +11986,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -12021,38 +12016,38 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="O59" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -12062,7 +12057,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -12077,7 +12072,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr">
@@ -12092,7 +12087,7 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
@@ -12112,12 +12107,12 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -12135,70 +12130,65 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -12230,12 +12220,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -12269,13 +12259,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O60" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R60" t="n">
-        <v>0.2299668573534158</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -12284,7 +12274,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -12304,7 +12294,7 @@
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
@@ -12314,7 +12304,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT60" t="n">
@@ -12322,47 +12312,47 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12394,12 +12384,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -12433,29 +12423,29 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O61" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -12480,7 +12470,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD61" t="inlineStr">
@@ -12515,17 +12505,17 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12543,7 +12533,7 @@
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
@@ -12553,7 +12543,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT61" t="n">
@@ -12561,47 +12551,47 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -12633,12 +12623,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -12672,13 +12662,13 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="O62" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="R62" t="n">
-        <v>0.3867666277328837</v>
+        <v>0.2299668573534158</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -12687,7 +12677,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -12702,7 +12692,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -12710,57 +12700,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -12792,12 +12787,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -12831,29 +12826,29 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="O63" t="n">
-        <v>89</v>
+        <v>13</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -12863,7 +12858,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -12878,7 +12873,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr">
@@ -12893,7 +12888,7 @@
       </c>
       <c r="AF63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG63" t="inlineStr">
@@ -12913,17 +12908,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -12936,7 +12931,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -12944,57 +12939,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13026,12 +13026,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -13056,22 +13056,22 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="O64" t="n">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="R64" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.3867666277328837</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -13095,70 +13095,65 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13190,12 +13185,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -13220,38 +13215,38 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="O65" t="n">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>HIV, total</t>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -13261,7 +13256,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -13276,7 +13271,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD65" t="inlineStr">
@@ -13291,7 +13286,7 @@
       </c>
       <c r="AF65" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG65" t="inlineStr">
@@ -13311,12 +13306,12 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
@@ -13334,70 +13329,65 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_150</t>
+          <t>SER_TW_HIV_044</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -13429,12 +13419,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -13468,13 +13458,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O66" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R66" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -13483,7 +13473,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -13503,7 +13493,7 @@
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
@@ -13513,7 +13503,7 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT66" t="n">
@@ -13521,47 +13511,47 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13583,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -13632,29 +13622,29 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O67" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Hiv-infeksjon</t>
+          <t>HIV, total</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
@@ -13679,7 +13669,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD67" t="inlineStr">
@@ -13714,17 +13704,17 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
         </is>
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -13742,7 +13732,7 @@
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR67" t="inlineStr">
@@ -13752,7 +13742,7 @@
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_902_MONTHLY</t>
+          <t>SER_FI_THL_TTR_150</t>
         </is>
       </c>
       <c r="AT67" t="n">
@@ -13760,47 +13750,47 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13832,12 +13822,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -13871,13 +13861,13 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="O68" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="R68" t="n">
-        <v>0.1607906205181651</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -13886,7 +13876,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -13901,7 +13891,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -13909,57 +13899,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -13991,12 +13986,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -14030,29 +14025,29 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="O69" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>SER_TW_HIV_044</t>
+          <t>SER_NO_FHI_902_MONTHLY</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+          <t>Hiv-infeksjon</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
@@ -14062,7 +14057,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -14077,7 +14072,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD69" t="inlineStr">
@@ -14092,7 +14087,7 @@
       </c>
       <c r="AF69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG69" t="inlineStr">
@@ -14112,17 +14107,17 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14135,65 +14130,1269 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA69" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB69" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC69" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N70" t="n">
+        <v>37</v>
+      </c>
+      <c r="O70" t="n">
+        <v>37</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.1607906205181651</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ69" t="inlineStr">
+      <c r="AQ70" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr">
+      <c r="AS70" t="inlineStr">
         <is>
           <t>SER_TW_HIV_044</t>
         </is>
       </c>
-      <c r="AT69" t="n">
+      <c r="AT70" t="n">
         <v>1</v>
       </c>
-      <c r="AU69" t="inlineStr">
+      <c r="AU70" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV69" t="inlineStr">
+      <c r="AV70" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="AW69" t="inlineStr">
+      <c r="AW70" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
+      <c r="AX70" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="AY69" t="inlineStr">
+      <c r="AY70" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
+      <c r="AZ70" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
         </is>
       </c>
-      <c r="BA69" t="inlineStr">
+      <c r="BA70" t="inlineStr">
         <is>
           <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
-      <c r="BB69" t="inlineStr">
+      <c r="BB70" t="inlineStr">
         <is>
           <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
-      <c r="BC69" t="inlineStr">
+      <c r="BC70" t="inlineStr">
         <is>
           <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>37</v>
+      </c>
+      <c r="O71" t="n">
+        <v>37</v>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS71" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AT71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA71" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB71" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC71" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA72" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB72" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC72" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>HIV, total</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL all-stage total; HIV not AIDS is an overlapping child and is not projected.</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_150</t>
+        </is>
+      </c>
+      <c r="AT73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA73" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB73" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC73" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP74" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ74" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA74" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB74" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC74" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>hiv-infection</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>D162</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>HIV infection</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>人类免疫缺乏病毒感染</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Hiv-infeksjon</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS HIV infection kept distinct from AIDS.</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ75" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_902_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA75" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB75" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC75" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -14230,7 +15429,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -14313,7 +15512,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -14323,7 +15522,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -14343,7 +15542,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -14375,7 +15574,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1376</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="16">
